--- a/data/Endeksler.xlsx
+++ b/data/Endeksler.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6582" uniqueCount="1452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6582" uniqueCount="1451">
   <si>
     <t>MAHALLEKAYITNO</t>
   </si>
@@ -4367,9 +4367,6 @@
   </si>
   <si>
     <t>YOĞUN KENT</t>
-  </si>
-  <si>
-    <t>ORTA YOĞUN KENT</t>
   </si>
 </sst>
 </file>
@@ -7294,7 +7291,7 @@
         <v>151</v>
       </c>
       <c r="E89" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F89">
         <v>216</v>
@@ -10374,7 +10371,7 @@
         <v>267</v>
       </c>
       <c r="E207" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F207">
         <v>1992</v>
@@ -10430,7 +10427,7 @@
         <v>268</v>
       </c>
       <c r="E208" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F208">
         <v>4033</v>
@@ -10586,7 +10583,7 @@
         <v>274</v>
       </c>
       <c r="E214" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F214">
         <v>596</v>
@@ -10910,7 +10907,7 @@
         <v>286</v>
       </c>
       <c r="E226" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F226">
         <v>3741</v>
@@ -11810,7 +11807,7 @@
         <v>328</v>
       </c>
       <c r="E268" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F268">
         <v>2928</v>
@@ -12158,7 +12155,7 @@
         <v>343</v>
       </c>
       <c r="E283" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F283">
         <v>1155</v>
@@ -12386,7 +12383,7 @@
         <v>352</v>
       </c>
       <c r="E292" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F292">
         <v>3949</v>
@@ -12938,7 +12935,7 @@
         <v>368</v>
       </c>
       <c r="E310" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F310">
         <v>1518</v>
@@ -13606,7 +13603,7 @@
         <v>388</v>
       </c>
       <c r="E335" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F335">
         <v>2091</v>
@@ -13694,7 +13691,7 @@
         <v>390</v>
       </c>
       <c r="E337" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F337">
         <v>1243</v>
@@ -13906,7 +13903,7 @@
         <v>397</v>
       </c>
       <c r="E344" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F344">
         <v>368</v>
@@ -15594,7 +15591,7 @@
         <v>118</v>
       </c>
       <c r="E405" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F405">
         <v>907</v>
@@ -15722,7 +15719,7 @@
         <v>457</v>
       </c>
       <c r="E409" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F409">
         <v>982</v>
@@ -15862,7 +15859,7 @@
         <v>460</v>
       </c>
       <c r="E413" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F413">
         <v>1717</v>
@@ -15998,7 +15995,7 @@
         <v>465</v>
       </c>
       <c r="E418" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F418">
         <v>5747</v>
@@ -16094,7 +16091,7 @@
         <v>204</v>
       </c>
       <c r="E421" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F421">
         <v>1814</v>
@@ -16150,7 +16147,7 @@
         <v>467</v>
       </c>
       <c r="E422" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F422">
         <v>2360</v>
@@ -16226,7 +16223,7 @@
         <v>469</v>
       </c>
       <c r="E424" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F424">
         <v>1087</v>
@@ -16486,7 +16483,7 @@
         <v>476</v>
       </c>
       <c r="E431" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F431">
         <v>2008</v>
@@ -16574,7 +16571,7 @@
         <v>478</v>
       </c>
       <c r="E433" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F433">
         <v>2073</v>
@@ -16714,7 +16711,7 @@
         <v>482</v>
       </c>
       <c r="E437" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F437">
         <v>9749</v>
@@ -16846,7 +16843,7 @@
         <v>485</v>
       </c>
       <c r="E440" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F440">
         <v>4636</v>
@@ -16998,7 +16995,7 @@
         <v>488</v>
       </c>
       <c r="E444" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F444">
         <v>2803</v>
@@ -17182,7 +17179,7 @@
         <v>142</v>
       </c>
       <c r="E449" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F449">
         <v>3708</v>
@@ -17350,7 +17347,7 @@
         <v>498</v>
       </c>
       <c r="E455" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F455">
         <v>6069</v>
@@ -17702,7 +17699,7 @@
         <v>509</v>
       </c>
       <c r="E466" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F466">
         <v>1394</v>
@@ -17814,7 +17811,7 @@
         <v>511</v>
       </c>
       <c r="E468" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F468">
         <v>10569</v>
@@ -18014,7 +18011,7 @@
         <v>514</v>
       </c>
       <c r="E472" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F472">
         <v>4647</v>
@@ -18210,7 +18207,7 @@
         <v>286</v>
       </c>
       <c r="E477" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F477">
         <v>6605</v>
@@ -18410,7 +18407,7 @@
         <v>521</v>
       </c>
       <c r="E481" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F481">
         <v>4670</v>
@@ -18486,7 +18483,7 @@
         <v>523</v>
       </c>
       <c r="E483" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F483">
         <v>10754</v>
@@ -18562,7 +18559,7 @@
         <v>525</v>
       </c>
       <c r="E485" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F485">
         <v>2493</v>
@@ -18678,7 +18675,7 @@
         <v>204</v>
       </c>
       <c r="E489" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F489">
         <v>12531</v>
@@ -21002,7 +20999,7 @@
         <v>580</v>
       </c>
       <c r="E550" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F550">
         <v>4682</v>
@@ -21366,7 +21363,7 @@
         <v>585</v>
       </c>
       <c r="E558" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F558">
         <v>4030</v>
@@ -21586,7 +21583,7 @@
         <v>590</v>
       </c>
       <c r="E563" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F563">
         <v>7384</v>
@@ -21770,7 +21767,7 @@
         <v>594</v>
       </c>
       <c r="E568" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F568">
         <v>490</v>
@@ -21810,7 +21807,7 @@
         <v>596</v>
       </c>
       <c r="E570" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F570">
         <v>1283</v>
@@ -22590,7 +22587,7 @@
         <v>610</v>
       </c>
       <c r="E585" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F585">
         <v>12449</v>
@@ -22810,7 +22807,7 @@
         <v>615</v>
       </c>
       <c r="E590" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F590">
         <v>5311</v>
@@ -24130,7 +24127,7 @@
         <v>118</v>
       </c>
       <c r="E620" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F620">
         <v>2762</v>
@@ -24658,7 +24655,7 @@
         <v>660</v>
       </c>
       <c r="E641" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F641">
         <v>1044</v>
@@ -24786,7 +24783,7 @@
         <v>204</v>
       </c>
       <c r="E645" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F645">
         <v>2080</v>
@@ -24882,7 +24879,7 @@
         <v>51</v>
       </c>
       <c r="E648" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F648">
         <v>1760</v>
@@ -24938,7 +24935,7 @@
         <v>666</v>
       </c>
       <c r="E649" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F649">
         <v>695</v>
@@ -25026,7 +25023,7 @@
         <v>668</v>
       </c>
       <c r="E651" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F651">
         <v>665</v>
@@ -25178,7 +25175,7 @@
         <v>672</v>
       </c>
       <c r="E655" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F655">
         <v>983</v>
@@ -25358,7 +25355,7 @@
         <v>498</v>
       </c>
       <c r="E661" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F661">
         <v>1302</v>
@@ -25642,7 +25639,7 @@
         <v>685</v>
       </c>
       <c r="E671" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F671">
         <v>628</v>
@@ -26126,7 +26123,7 @@
         <v>101</v>
       </c>
       <c r="E682" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F682">
         <v>1789</v>
@@ -26786,7 +26783,7 @@
         <v>706</v>
       </c>
       <c r="E700" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F700">
         <v>2691</v>
@@ -26842,7 +26839,7 @@
         <v>707</v>
       </c>
       <c r="E701" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F701">
         <v>5251</v>
@@ -26898,7 +26895,7 @@
         <v>708</v>
       </c>
       <c r="E702" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F702">
         <v>4760</v>
@@ -26994,7 +26991,7 @@
         <v>711</v>
       </c>
       <c r="E705" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F705">
         <v>3377</v>
@@ -27070,7 +27067,7 @@
         <v>574</v>
       </c>
       <c r="E707" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F707">
         <v>2093</v>
@@ -27126,7 +27123,7 @@
         <v>713</v>
       </c>
       <c r="E708" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F708">
         <v>2265</v>
@@ -27298,7 +27295,7 @@
         <v>717</v>
       </c>
       <c r="E713" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F713">
         <v>1968</v>
@@ -27410,7 +27407,7 @@
         <v>719</v>
       </c>
       <c r="E715" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F715">
         <v>657</v>
@@ -27466,7 +27463,7 @@
         <v>720</v>
       </c>
       <c r="E716" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F716">
         <v>789</v>
@@ -28650,7 +28647,7 @@
         <v>743</v>
       </c>
       <c r="E747" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F747">
         <v>3167</v>
@@ -28706,7 +28703,7 @@
         <v>744</v>
       </c>
       <c r="E748" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F748">
         <v>1887</v>
@@ -28990,7 +28987,7 @@
         <v>750</v>
       </c>
       <c r="E755" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F755">
         <v>2855</v>
@@ -29426,7 +29423,7 @@
         <v>760</v>
       </c>
       <c r="E766" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F766">
         <v>1666</v>
@@ -29482,7 +29479,7 @@
         <v>761</v>
       </c>
       <c r="E767" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F767">
         <v>2907</v>
@@ -30102,7 +30099,7 @@
         <v>132</v>
       </c>
       <c r="E783" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F783">
         <v>2370</v>
@@ -30310,7 +30307,7 @@
         <v>78</v>
       </c>
       <c r="E788" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F788">
         <v>1986</v>
@@ -30366,7 +30363,7 @@
         <v>79</v>
       </c>
       <c r="E789" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F789">
         <v>1903</v>
@@ -30998,7 +30995,7 @@
         <v>792</v>
       </c>
       <c r="E805" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F805">
         <v>6317</v>
@@ -31054,7 +31051,7 @@
         <v>793</v>
       </c>
       <c r="E806" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F806">
         <v>1948</v>
@@ -31222,7 +31219,7 @@
         <v>118</v>
       </c>
       <c r="E812" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F812">
         <v>3994</v>
@@ -31298,7 +31295,7 @@
         <v>535</v>
       </c>
       <c r="E814" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F814">
         <v>4009</v>
@@ -31374,7 +31371,7 @@
         <v>142</v>
       </c>
       <c r="E816" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F816">
         <v>6745</v>
@@ -31574,7 +31571,7 @@
         <v>804</v>
       </c>
       <c r="E823" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F823">
         <v>1091</v>
@@ -31670,7 +31667,7 @@
         <v>807</v>
       </c>
       <c r="E826" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F826">
         <v>1500</v>
@@ -31858,7 +31855,7 @@
         <v>814</v>
       </c>
       <c r="E833" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F833">
         <v>537</v>
@@ -31914,7 +31911,7 @@
         <v>815</v>
       </c>
       <c r="E834" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F834">
         <v>2359</v>
@@ -31970,7 +31967,7 @@
         <v>816</v>
       </c>
       <c r="E835" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F835">
         <v>1245</v>
@@ -32026,7 +32023,7 @@
         <v>817</v>
       </c>
       <c r="E836" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F836">
         <v>2839</v>
@@ -32114,7 +32111,7 @@
         <v>51</v>
       </c>
       <c r="E838" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F838">
         <v>1651</v>
@@ -32170,7 +32167,7 @@
         <v>691</v>
       </c>
       <c r="E839" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F839">
         <v>3372</v>
@@ -32366,7 +32363,7 @@
         <v>821</v>
       </c>
       <c r="E844" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F844">
         <v>1522</v>
@@ -32530,7 +32527,7 @@
         <v>824</v>
       </c>
       <c r="E848" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F848">
         <v>891</v>
@@ -32642,7 +32639,7 @@
         <v>698</v>
       </c>
       <c r="E850" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F850">
         <v>1011</v>
@@ -32698,7 +32695,7 @@
         <v>118</v>
       </c>
       <c r="E851" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F851">
         <v>3247</v>
@@ -32754,7 +32751,7 @@
         <v>826</v>
       </c>
       <c r="E852" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F852">
         <v>1635</v>
@@ -32842,7 +32839,7 @@
         <v>127</v>
       </c>
       <c r="E854" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F854">
         <v>1120</v>
@@ -32950,7 +32947,7 @@
         <v>384</v>
       </c>
       <c r="E857" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F857">
         <v>1855</v>
@@ -33250,7 +33247,7 @@
         <v>142</v>
       </c>
       <c r="E863" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F863">
         <v>3342</v>
@@ -33338,7 +33335,7 @@
         <v>834</v>
       </c>
       <c r="E865" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F865">
         <v>1494</v>
@@ -33394,7 +33391,7 @@
         <v>835</v>
       </c>
       <c r="E866" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F866">
         <v>827</v>
@@ -33450,7 +33447,7 @@
         <v>836</v>
       </c>
       <c r="E867" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F867">
         <v>1497</v>
@@ -33506,7 +33503,7 @@
         <v>837</v>
       </c>
       <c r="E868" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F868">
         <v>11080</v>
@@ -33562,7 +33559,7 @@
         <v>838</v>
       </c>
       <c r="E869" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F869">
         <v>2162</v>
@@ -33618,7 +33615,7 @@
         <v>839</v>
       </c>
       <c r="E870" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F870">
         <v>603</v>
@@ -33674,7 +33671,7 @@
         <v>840</v>
       </c>
       <c r="E871" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F871">
         <v>2519</v>
@@ -34306,7 +34303,7 @@
         <v>61</v>
       </c>
       <c r="E884" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F884">
         <v>1955</v>
@@ -34526,7 +34523,7 @@
         <v>853</v>
       </c>
       <c r="E889" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F889">
         <v>2558</v>
@@ -34638,7 +34635,7 @@
         <v>855</v>
       </c>
       <c r="E891" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F891">
         <v>11043</v>
@@ -34694,7 +34691,7 @@
         <v>856</v>
       </c>
       <c r="E892" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F892">
         <v>16172</v>
@@ -34918,7 +34915,7 @@
         <v>860</v>
       </c>
       <c r="E896" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F896">
         <v>1165</v>
@@ -35030,7 +35027,7 @@
         <v>359</v>
       </c>
       <c r="E898" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F898">
         <v>2001</v>
@@ -35086,7 +35083,7 @@
         <v>51</v>
       </c>
       <c r="E899" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F899">
         <v>3193</v>
@@ -35162,7 +35159,7 @@
         <v>863</v>
       </c>
       <c r="E901" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F901">
         <v>469</v>
@@ -35234,7 +35231,7 @@
         <v>256</v>
       </c>
       <c r="E904" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F904">
         <v>2271</v>
@@ -35290,7 +35287,7 @@
         <v>556</v>
       </c>
       <c r="E905" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F905">
         <v>1018</v>
@@ -35462,7 +35459,7 @@
         <v>132</v>
       </c>
       <c r="E910" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F910">
         <v>1981</v>
@@ -35602,7 +35599,7 @@
         <v>872</v>
       </c>
       <c r="E914" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F914">
         <v>2740</v>
@@ -35742,7 +35739,7 @@
         <v>876</v>
       </c>
       <c r="E918" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F918">
         <v>4729</v>
@@ -35798,7 +35795,7 @@
         <v>877</v>
       </c>
       <c r="E919" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F919">
         <v>1528</v>
@@ -35874,7 +35871,7 @@
         <v>879</v>
       </c>
       <c r="E921" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F921">
         <v>478</v>
@@ -35958,7 +35955,7 @@
         <v>882</v>
       </c>
       <c r="E924" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F924">
         <v>390</v>
@@ -36050,7 +36047,7 @@
         <v>886</v>
       </c>
       <c r="E928" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F928">
         <v>1198</v>
@@ -36198,7 +36195,7 @@
         <v>890</v>
       </c>
       <c r="E933" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F933">
         <v>2191</v>
@@ -36294,7 +36291,7 @@
         <v>893</v>
       </c>
       <c r="E936" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F936">
         <v>3917</v>
@@ -36370,7 +36367,7 @@
         <v>894</v>
       </c>
       <c r="E938" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F938">
         <v>1577</v>
@@ -36426,7 +36423,7 @@
         <v>61</v>
       </c>
       <c r="E939" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F939">
         <v>966</v>
@@ -36502,7 +36499,7 @@
         <v>896</v>
       </c>
       <c r="E941" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F941">
         <v>1763</v>
@@ -36558,7 +36555,7 @@
         <v>628</v>
       </c>
       <c r="E942" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F942">
         <v>5458</v>
@@ -36614,7 +36611,7 @@
         <v>520</v>
       </c>
       <c r="E943" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F943">
         <v>1967</v>
@@ -36802,7 +36799,7 @@
         <v>903</v>
       </c>
       <c r="E950" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F950">
         <v>735</v>
@@ -36910,7 +36907,7 @@
         <v>905</v>
       </c>
       <c r="E953" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F953">
         <v>2519</v>
@@ -36966,7 +36963,7 @@
         <v>101</v>
       </c>
       <c r="E954" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F954">
         <v>863</v>
@@ -37022,7 +37019,7 @@
         <v>118</v>
       </c>
       <c r="E955" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F955">
         <v>2346</v>
@@ -37130,7 +37127,7 @@
         <v>908</v>
       </c>
       <c r="E958" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F958">
         <v>371</v>
@@ -37150,7 +37147,7 @@
         <v>142</v>
       </c>
       <c r="E959" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F959">
         <v>2234</v>
@@ -37246,7 +37243,7 @@
         <v>910</v>
       </c>
       <c r="E962" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F962">
         <v>1173</v>
@@ -37342,7 +37339,7 @@
         <v>286</v>
       </c>
       <c r="E965" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F965">
         <v>1032</v>
@@ -37562,7 +37559,7 @@
         <v>920</v>
       </c>
       <c r="E973" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F973">
         <v>1005</v>
@@ -37730,7 +37727,7 @@
         <v>926</v>
       </c>
       <c r="E979" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F979">
         <v>1368</v>
@@ -37786,7 +37783,7 @@
         <v>927</v>
       </c>
       <c r="E980" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F980">
         <v>1705</v>
@@ -37914,7 +37911,7 @@
         <v>930</v>
       </c>
       <c r="E984" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F984">
         <v>727</v>
@@ -37990,7 +37987,7 @@
         <v>910</v>
       </c>
       <c r="E986" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F986">
         <v>6038</v>
@@ -38066,7 +38063,7 @@
         <v>933</v>
       </c>
       <c r="E988" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F988">
         <v>1123</v>
@@ -38206,7 +38203,7 @@
         <v>937</v>
       </c>
       <c r="E992" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F992">
         <v>506</v>
@@ -38262,7 +38259,7 @@
         <v>938</v>
       </c>
       <c r="E993" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F993">
         <v>844</v>
@@ -38318,7 +38315,7 @@
         <v>939</v>
       </c>
       <c r="E994" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F994">
         <v>1975</v>
@@ -38374,7 +38371,7 @@
         <v>817</v>
       </c>
       <c r="E995" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F995">
         <v>1275</v>
@@ -38430,7 +38427,7 @@
         <v>51</v>
       </c>
       <c r="E996" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F996">
         <v>16108</v>
@@ -38506,7 +38503,7 @@
         <v>940</v>
       </c>
       <c r="E998" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F998">
         <v>15824</v>
@@ -38594,7 +38591,7 @@
         <v>942</v>
       </c>
       <c r="E1000" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1000">
         <v>7911</v>
@@ -38734,7 +38731,7 @@
         <v>558</v>
       </c>
       <c r="E1004" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1004">
         <v>1256</v>
@@ -38906,7 +38903,7 @@
         <v>948</v>
       </c>
       <c r="E1009" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1009">
         <v>2336</v>
@@ -39034,7 +39031,7 @@
         <v>535</v>
       </c>
       <c r="E1013" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1013">
         <v>662</v>
@@ -39318,7 +39315,7 @@
         <v>960</v>
       </c>
       <c r="E1023" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1023">
         <v>927</v>
@@ -39406,7 +39403,7 @@
         <v>962</v>
       </c>
       <c r="E1025" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1025">
         <v>1724</v>
@@ -39462,7 +39459,7 @@
         <v>963</v>
       </c>
       <c r="E1026" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1026">
         <v>14337</v>
@@ -39614,7 +39611,7 @@
         <v>967</v>
       </c>
       <c r="E1030" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1030">
         <v>4859</v>
@@ -39690,7 +39687,7 @@
         <v>589</v>
       </c>
       <c r="E1032" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1032">
         <v>7014</v>
@@ -39850,7 +39847,7 @@
         <v>973</v>
       </c>
       <c r="E1037" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1037">
         <v>2977</v>
@@ -39906,7 +39903,7 @@
         <v>910</v>
       </c>
       <c r="E1038" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1038">
         <v>14902</v>
@@ -39962,7 +39959,7 @@
         <v>974</v>
       </c>
       <c r="E1039" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1039">
         <v>887</v>
@@ -40166,7 +40163,7 @@
         <v>980</v>
       </c>
       <c r="E1045" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1045">
         <v>1826</v>
@@ -40254,7 +40251,7 @@
         <v>982</v>
       </c>
       <c r="E1047" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1047">
         <v>2777</v>
@@ -40350,7 +40347,7 @@
         <v>983</v>
       </c>
       <c r="E1050" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1050">
         <v>12416</v>
@@ -40406,7 +40403,7 @@
         <v>984</v>
       </c>
       <c r="E1051" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1051">
         <v>2789</v>
@@ -40482,7 +40479,7 @@
         <v>986</v>
       </c>
       <c r="E1053" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1053">
         <v>1039</v>
@@ -40578,7 +40575,7 @@
         <v>989</v>
       </c>
       <c r="E1056" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1056">
         <v>2413</v>
@@ -40686,7 +40683,7 @@
         <v>992</v>
       </c>
       <c r="E1059" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1059">
         <v>5661</v>
@@ -40742,7 +40739,7 @@
         <v>993</v>
       </c>
       <c r="E1060" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1060">
         <v>1108</v>
@@ -40934,7 +40931,7 @@
         <v>51</v>
       </c>
       <c r="E1066" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1066">
         <v>2119</v>
@@ -41062,7 +41059,7 @@
         <v>472</v>
       </c>
       <c r="E1070" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1070">
         <v>1973</v>
@@ -41370,7 +41367,7 @@
         <v>1013</v>
       </c>
       <c r="E1083" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1083">
         <v>1571</v>
@@ -41682,7 +41679,7 @@
         <v>890</v>
       </c>
       <c r="E1095" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1095">
         <v>2672</v>
@@ -42186,7 +42183,7 @@
         <v>1043</v>
       </c>
       <c r="E1116" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1116">
         <v>7184</v>
@@ -42330,7 +42327,7 @@
         <v>1044</v>
       </c>
       <c r="E1119" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1119">
         <v>889</v>
@@ -42494,7 +42491,7 @@
         <v>118</v>
       </c>
       <c r="E1123" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1123">
         <v>2568</v>
@@ -42550,7 +42547,7 @@
         <v>1047</v>
       </c>
       <c r="E1124" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1124">
         <v>2481</v>
@@ -42626,7 +42623,7 @@
         <v>1049</v>
       </c>
       <c r="E1126" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1126">
         <v>14261</v>
@@ -42734,7 +42731,7 @@
         <v>1052</v>
       </c>
       <c r="E1129" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1129">
         <v>1251</v>
@@ -42934,7 +42931,7 @@
         <v>142</v>
       </c>
       <c r="E1133" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1133">
         <v>1157</v>
@@ -43338,7 +43335,7 @@
         <v>1062</v>
       </c>
       <c r="E1143" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1143">
         <v>5094</v>
@@ -43414,7 +43411,7 @@
         <v>1064</v>
       </c>
       <c r="E1145" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1145">
         <v>1418</v>
@@ -43786,7 +43783,7 @@
         <v>204</v>
       </c>
       <c r="E1154" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1154">
         <v>4556</v>
@@ -43978,7 +43975,7 @@
         <v>1074</v>
       </c>
       <c r="E1160" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1160">
         <v>827</v>
@@ -44114,7 +44111,7 @@
         <v>118</v>
       </c>
       <c r="E1165" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1165">
         <v>3579</v>
@@ -44250,7 +44247,7 @@
         <v>1080</v>
       </c>
       <c r="E1170" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1170">
         <v>3887</v>
@@ -44306,7 +44303,7 @@
         <v>1081</v>
       </c>
       <c r="E1171" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1171">
         <v>3682</v>
@@ -44606,7 +44603,7 @@
         <v>1092</v>
       </c>
       <c r="E1183" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1183">
         <v>3740</v>
@@ -44986,7 +44983,7 @@
         <v>1103</v>
       </c>
       <c r="E1199" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1199">
         <v>827</v>
@@ -45082,7 +45079,7 @@
         <v>267</v>
       </c>
       <c r="E1202" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1202">
         <v>3357</v>
@@ -45218,7 +45215,7 @@
         <v>1108</v>
       </c>
       <c r="E1207" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1207">
         <v>561</v>
@@ -45458,7 +45455,7 @@
         <v>841</v>
       </c>
       <c r="E1216" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1216">
         <v>2329</v>
@@ -45534,7 +45531,7 @@
         <v>598</v>
       </c>
       <c r="E1218" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1218">
         <v>3789</v>
@@ -45742,7 +45739,7 @@
         <v>974</v>
       </c>
       <c r="E1226" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1226">
         <v>3263</v>
@@ -46058,7 +46055,7 @@
         <v>1130</v>
       </c>
       <c r="E1237" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1237">
         <v>1782</v>
@@ -46114,7 +46111,7 @@
         <v>1131</v>
       </c>
       <c r="E1238" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1238">
         <v>2340</v>
@@ -46626,7 +46623,7 @@
         <v>692</v>
       </c>
       <c r="E1260" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1260">
         <v>9194</v>
@@ -46682,7 +46679,7 @@
         <v>1149</v>
       </c>
       <c r="E1261" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1261">
         <v>6760</v>
@@ -46894,7 +46891,7 @@
         <v>1155</v>
       </c>
       <c r="E1268" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1268">
         <v>1046</v>
@@ -47006,7 +47003,7 @@
         <v>1157</v>
       </c>
       <c r="E1270" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1270">
         <v>939</v>
@@ -47526,7 +47523,7 @@
         <v>1171</v>
       </c>
       <c r="E1287" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1287">
         <v>940</v>
@@ -48554,7 +48551,7 @@
         <v>1202</v>
       </c>
       <c r="E1321" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1321">
         <v>19001</v>
@@ -48666,7 +48663,7 @@
         <v>1203</v>
       </c>
       <c r="E1323" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1323">
         <v>1252</v>
@@ -49370,7 +49367,7 @@
         <v>1222</v>
       </c>
       <c r="E1348" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1348">
         <v>1615</v>
@@ -49630,7 +49627,7 @@
         <v>1227</v>
       </c>
       <c r="E1355" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1355">
         <v>956</v>
@@ -50882,7 +50879,7 @@
         <v>710</v>
       </c>
       <c r="E1393" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1393">
         <v>502</v>
@@ -51850,7 +51847,7 @@
         <v>1278</v>
       </c>
       <c r="E1418" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1418">
         <v>602</v>
@@ -53166,7 +53163,7 @@
         <v>1318</v>
       </c>
       <c r="E1467" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1467">
         <v>864</v>
@@ -53850,7 +53847,7 @@
         <v>754</v>
       </c>
       <c r="E1488" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1488">
         <v>8415</v>
@@ -54002,7 +53999,7 @@
         <v>626</v>
       </c>
       <c r="E1492" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1492">
         <v>1794</v>
@@ -54146,7 +54143,7 @@
         <v>759</v>
       </c>
       <c r="E1495" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1495">
         <v>2337</v>
@@ -54762,7 +54759,7 @@
         <v>1356</v>
       </c>
       <c r="E1518" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1518">
         <v>625</v>
@@ -55338,7 +55335,7 @@
         <v>1366</v>
       </c>
       <c r="E1530" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1530">
         <v>8959</v>
@@ -59022,7 +59019,7 @@
         <v>1433</v>
       </c>
       <c r="E1620" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F1620">
         <v>1202</v>
